--- a/tests/text archivo ej 01.xlsx
+++ b/tests/text archivo ej 01.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="69">
   <si>
     <t xml:space="preserve">IMPORTACIÓN DE TEXTURA – EJEMPLO</t>
   </si>
@@ -118,6 +118,9 @@
     <t xml:space="preserve">24.2</t>
   </si>
   <si>
+    <t xml:space="preserve">12.40</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.28</t>
   </si>
   <si>
@@ -188,9 +191,6 @@
   </si>
   <si>
     <t xml:space="preserve">20.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.40</t>
   </si>
   <si>
     <t xml:space="preserve">19.8</t>
@@ -459,7 +459,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.2"/>
@@ -675,377 +675,424 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>1439</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>245</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>238</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>224</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="L7" s="1" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>1443</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>242</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>234</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>226</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>220</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="L8" s="1" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>1440</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>242</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>234</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="1" t="n">
-        <v>248</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>240</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>233</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>227</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="L9" s="1" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>1437</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>248</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>239</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>232</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>225</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>219</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="L10" s="1" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>1442</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>239</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="1" t="n">
-        <v>244</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>236</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>228</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>221</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" s="1" t="s">
+      <c r="L11" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="M11" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L11" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="M11" s="1" t="n">
-        <v>60</v>
-      </c>
       <c r="N11" s="1" t="n">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>1439</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>237</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>359</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>246</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E14" s="1" t="n">
         <v>239</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="F14" s="1" t="n">
         <v>231</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="G14" s="1" t="n">
         <v>224</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="L13" s="1" t="n">
+      <c r="L14" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="M13" s="1" t="n">
+      <c r="M14" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="N13" s="1" t="n">
+      <c r="N14" s="1" t="n">
         <v>360</v>
       </c>
-      <c r="O13" s="1" t="n">
+      <c r="O14" s="1" t="n">
         <v>1441</v>
       </c>
     </row>

--- a/tests/text archivo ej 01.xlsx
+++ b/tests/text archivo ej 01.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="112">
   <si>
     <t xml:space="preserve">IMPORTACIÓN DE TEXTURA – EJEMPLO</t>
   </si>
@@ -76,6 +76,18 @@
     <t xml:space="preserve">12.50</t>
   </si>
   <si>
+    <t xml:space="preserve">5.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9</t>
+  </si>
+  <si>
     <t xml:space="preserve">24.8</t>
   </si>
   <si>
@@ -91,6 +103,18 @@
     <t xml:space="preserve">12.34</t>
   </si>
   <si>
+    <t xml:space="preserve">32.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9</t>
+  </si>
+  <si>
     <t xml:space="preserve">23.5</t>
   </si>
   <si>
@@ -106,6 +130,18 @@
     <t xml:space="preserve">12.41</t>
   </si>
   <si>
+    <t xml:space="preserve">40.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4</t>
+  </si>
+  <si>
     <t xml:space="preserve">24.1</t>
   </si>
   <si>
@@ -121,9 +157,33 @@
     <t xml:space="preserve">12.40</t>
   </si>
   <si>
+    <t xml:space="preserve">38.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.28</t>
   </si>
   <si>
+    <t xml:space="preserve">52.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8</t>
+  </si>
+  <si>
     <t xml:space="preserve">22.9</t>
   </si>
   <si>
@@ -139,33 +199,60 @@
     <t xml:space="preserve">12.37</t>
   </si>
   <si>
+    <t xml:space="preserve">27.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">25.2</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3</t>
-  </si>
-  <si>
     <t xml:space="preserve">25.4</t>
   </si>
   <si>
     <t xml:space="preserve">12.45</t>
   </si>
   <si>
+    <t xml:space="preserve">45.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6</t>
+  </si>
+  <si>
     <t xml:space="preserve">21.8</t>
   </si>
   <si>
     <t xml:space="preserve">22.0</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9</t>
-  </si>
-  <si>
     <t xml:space="preserve">22.1</t>
   </si>
   <si>
     <t xml:space="preserve">12.30</t>
   </si>
   <si>
+    <t xml:space="preserve">58.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.0</t>
   </si>
   <si>
@@ -181,6 +268,15 @@
     <t xml:space="preserve">12.36</t>
   </si>
   <si>
+    <t xml:space="preserve">34.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4</t>
+  </si>
+  <si>
     <t xml:space="preserve">20.5</t>
   </si>
   <si>
@@ -193,6 +289,18 @@
     <t xml:space="preserve">20.8</t>
   </si>
   <si>
+    <t xml:space="preserve">47.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7</t>
+  </si>
+  <si>
     <t xml:space="preserve">19.8</t>
   </si>
   <si>
@@ -208,6 +316,15 @@
     <t xml:space="preserve">12.33</t>
   </si>
   <si>
+    <t xml:space="preserve">19.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6</t>
+  </si>
+  <si>
     <t xml:space="preserve">23.2</t>
   </si>
   <si>
@@ -215,6 +332,18 @@
   </si>
   <si>
     <t xml:space="preserve">12.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4</t>
   </si>
   <si>
     <t xml:space="preserve">24.4</t>
@@ -236,7 +365,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -268,6 +397,13 @@
     <font>
       <b val="true"/>
       <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -315,7 +451,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -334,6 +470,14 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -356,37 +500,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -459,7 +603,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.2"/>
@@ -533,38 +677,38 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>220</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>215</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>210</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>205</v>
+      <c r="D3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L3" s="1" t="n">
         <v>29</v>
@@ -580,38 +724,38 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="5" t="n">
         <v>1001</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>235</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>228</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>220</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>215</v>
+      <c r="C4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L4" s="1" t="n">
         <v>30</v>
@@ -627,38 +771,38 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="5" t="n">
         <v>1002</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>240</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>232</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>225</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>219</v>
+      <c r="C5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="L5" s="1" t="n">
         <v>31</v>
@@ -674,38 +818,38 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="5" t="n">
         <v>1002</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>239</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>232</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>215</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>220</v>
+      <c r="C6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>32</v>
@@ -721,38 +865,38 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="5" t="n">
         <v>1003</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>245</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>238</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>230</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>222</v>
+      <c r="C7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>29</v>
@@ -768,38 +912,38 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="5" t="n">
         <v>1004</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>238</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>224</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>218</v>
+      <c r="C8" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>30</v>
@@ -815,38 +959,38 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="5" t="n">
         <v>1005</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>242</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>234</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>226</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>220</v>
+      <c r="C9" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="L9" s="1" t="n">
         <v>32</v>
@@ -862,38 +1006,38 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="5" t="n">
         <v>1006</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>248</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>240</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>233</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>227</v>
+      <c r="C10" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="L10" s="1" t="n">
         <v>28</v>
@@ -909,38 +1053,38 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="5" t="n">
         <v>1007</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>239</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>232</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>225</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>219</v>
+      <c r="C11" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="L11" s="1" t="n">
         <v>30</v>
@@ -956,38 +1100,38 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="5" t="n">
         <v>1008</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>244</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>236</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>228</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>221</v>
+      <c r="C12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="L12" s="1" t="n">
         <v>31</v>
@@ -1003,38 +1147,38 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="5" t="n">
         <v>1009</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>237</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>229</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>222</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>216</v>
+      <c r="C13" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="L13" s="1" t="n">
         <v>29</v>
@@ -1050,38 +1194,38 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="5" t="n">
         <v>1010</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>246</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>239</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>224</v>
+      <c r="C14" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="L14" s="1" t="n">
         <v>30</v>
@@ -1095,6 +1239,123 @@
       <c r="O14" s="1" t="n">
         <v>1441</v>
       </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/tests/text archivo ej 01.xlsx
+++ b/tests/text archivo ej 01.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="69">
   <si>
     <t xml:space="preserve">IMPORTACIÓN DE TEXTURA – EJEMPLO</t>
   </si>
@@ -76,18 +76,6 @@
     <t xml:space="preserve">12.50</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9</t>
-  </si>
-  <si>
     <t xml:space="preserve">24.8</t>
   </si>
   <si>
@@ -103,156 +91,81 @@
     <t xml:space="preserve">12.34</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7</t>
+    <t xml:space="preserve">23.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2</t>
   </si>
   <si>
     <t xml:space="preserve">25.3</t>
   </si>
   <si>
+    <t xml:space="preserve">25.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">21.9</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0</t>
-  </si>
-  <si>
     <t xml:space="preserve">22.1</t>
   </si>
   <si>
     <t xml:space="preserve">12.30</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.0</t>
   </si>
   <si>
@@ -268,15 +181,6 @@
     <t xml:space="preserve">12.36</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4</t>
-  </si>
-  <si>
     <t xml:space="preserve">20.5</t>
   </si>
   <si>
@@ -289,18 +193,6 @@
     <t xml:space="preserve">20.8</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7</t>
-  </si>
-  <si>
     <t xml:space="preserve">19.8</t>
   </si>
   <si>
@@ -316,15 +208,6 @@
     <t xml:space="preserve">12.33</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6</t>
-  </si>
-  <si>
     <t xml:space="preserve">23.2</t>
   </si>
   <si>
@@ -332,18 +215,6 @@
   </si>
   <si>
     <t xml:space="preserve">12.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4</t>
   </si>
   <si>
     <t xml:space="preserve">24.4</t>
@@ -365,7 +236,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -397,13 +268,6 @@
     <font>
       <b val="true"/>
       <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -451,7 +315,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -470,14 +334,6 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -500,37 +356,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18A303"/>
+        <a:srgbClr val="18a303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369A3"/>
+        <a:srgbClr val="0369a3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A33E03"/>
+        <a:srgbClr val="a33e03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8E03A3"/>
+        <a:srgbClr val="8e03a3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C99C00"/>
+        <a:srgbClr val="c99c00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C9211E"/>
+        <a:srgbClr val="c9211e"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000EE"/>
+        <a:srgbClr val="0000ee"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551A8B"/>
+        <a:srgbClr val="551a8b"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -603,7 +459,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.2"/>
@@ -677,38 +533,38 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="I3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="J3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="K3" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="L3" s="1" t="n">
         <v>29</v>
@@ -724,38 +580,38 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="1" t="n">
         <v>1001</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="L4" s="1" t="n">
         <v>30</v>
@@ -771,38 +627,38 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="1" t="n">
         <v>1002</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>39</v>
+      <c r="C5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>219</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="L5" s="1" t="n">
         <v>31</v>
@@ -818,38 +674,38 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="1" t="n">
         <v>1002</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>48</v>
+      <c r="C6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>239</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>220</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>32</v>
@@ -865,38 +721,38 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="1" t="n">
         <v>1003</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>53</v>
+      <c r="C7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>245</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>222</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>29</v>
@@ -912,38 +768,38 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="1" t="n">
         <v>1004</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>61</v>
+      <c r="C8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>218</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>30</v>
@@ -959,38 +815,38 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="1" t="n">
         <v>1005</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>68</v>
+      <c r="C9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>242</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>234</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>220</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="L9" s="1" t="n">
         <v>32</v>
@@ -1006,38 +862,38 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="1" t="n">
         <v>1006</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>76</v>
+      <c r="C10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>248</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>227</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="L10" s="1" t="n">
         <v>28</v>
@@ -1053,38 +909,38 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="1" t="n">
         <v>1007</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>22</v>
+      <c r="C11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>239</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>219</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="L11" s="1" t="n">
         <v>30</v>
@@ -1100,38 +956,38 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="1" t="n">
         <v>1008</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>92</v>
+      <c r="C12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>236</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>221</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="L12" s="1" t="n">
         <v>31</v>
@@ -1147,38 +1003,38 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="1" t="n">
         <v>1009</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>100</v>
+      <c r="C13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>237</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>216</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="L13" s="1" t="n">
         <v>29</v>
@@ -1194,38 +1050,38 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="1" t="n">
         <v>1010</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>107</v>
+      <c r="C14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>246</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>239</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>224</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="L14" s="1" t="n">
         <v>30</v>
@@ -1239,123 +1095,6 @@
       <c r="O14" s="1" t="n">
         <v>1441</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/tests/text archivo ej 01.xlsx
+++ b/tests/text archivo ej 01.xlsx
@@ -356,37 +356,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">

--- a/tests/text archivo ej 01.xlsx
+++ b/tests/text archivo ej 01.xlsx
@@ -236,7 +236,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -268,6 +268,13 @@
     <font>
       <b val="true"/>
       <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -315,7 +322,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -334,6 +341,14 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -356,37 +371,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18A303"/>
+        <a:srgbClr val="18a303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369A3"/>
+        <a:srgbClr val="0369a3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A33E03"/>
+        <a:srgbClr val="a33e03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8E03A3"/>
+        <a:srgbClr val="8e03a3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C99C00"/>
+        <a:srgbClr val="c99c00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C9211E"/>
+        <a:srgbClr val="c9211e"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000EE"/>
+        <a:srgbClr val="0000ee"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551A8B"/>
+        <a:srgbClr val="551a8b"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -459,7 +474,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.2"/>
@@ -572,11 +587,11 @@
       <c r="M3" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="N3" s="1" t="n">
-        <v>358</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>1442</v>
+      <c r="N3" s="5" t="n">
+        <v>21480</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>86520</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -619,11 +634,11 @@
       <c r="M4" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="N4" s="1" t="n">
-        <v>362</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>1438</v>
+      <c r="N4" s="5" t="n">
+        <v>21720</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>86280</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -666,11 +681,11 @@
       <c r="M5" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="N5" s="1" t="n">
-        <v>359</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>1441</v>
+      <c r="N5" s="5" t="n">
+        <v>21540</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>86460</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -713,11 +728,11 @@
       <c r="M6" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="N6" s="1" t="n">
-        <v>358</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>1438</v>
+      <c r="N6" s="5" t="n">
+        <v>21480</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>86280</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -760,11 +775,11 @@
       <c r="M7" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="N7" s="1" t="n">
-        <v>361</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>1439</v>
+      <c r="N7" s="5" t="n">
+        <v>21660</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>86340</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -807,11 +822,11 @@
       <c r="M8" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="N8" s="1" t="n">
-        <v>357</v>
-      </c>
-      <c r="O8" s="1" t="n">
-        <v>1443</v>
+      <c r="N8" s="5" t="n">
+        <v>21420</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>86580</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -854,11 +869,11 @@
       <c r="M9" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="N9" s="1" t="n">
-        <v>363</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>1440</v>
+      <c r="N9" s="5" t="n">
+        <v>21780</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>86400</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -901,11 +916,11 @@
       <c r="M10" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="N10" s="1" t="n">
-        <v>360</v>
-      </c>
-      <c r="O10" s="1" t="n">
-        <v>1437</v>
+      <c r="N10" s="5" t="n">
+        <v>21600</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>86220</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -948,11 +963,11 @@
       <c r="M11" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="N11" s="1" t="n">
-        <v>358</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>1442</v>
+      <c r="N11" s="5" t="n">
+        <v>21480</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>86520</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -995,11 +1010,11 @@
       <c r="M12" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="N12" s="1" t="n">
-        <v>361</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <v>1444</v>
+      <c r="N12" s="5" t="n">
+        <v>21660</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>86640</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1042,11 +1057,11 @@
       <c r="M13" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="N13" s="1" t="n">
-        <v>359</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>1439</v>
+      <c r="N13" s="5" t="n">
+        <v>21540</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>86340</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1089,12 +1104,90 @@
       <c r="M14" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="N14" s="1" t="n">
-        <v>360</v>
-      </c>
-      <c r="O14" s="1" t="n">
-        <v>1441</v>
-      </c>
+      <c r="N14" s="5" t="n">
+        <v>21600</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>86460</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
